--- a/artfynd/A 23257-2026 artfynd.xlsx
+++ b/artfynd/A 23257-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80686732</v>
+        <v>1913285</v>
       </c>
       <c r="B2" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100067</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storsjön, Bergby, Gstr</t>
+          <t>(14H1c17), Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606166.2042321098</v>
+        <v>606650</v>
       </c>
       <c r="R2" t="n">
-        <v>6757514.204987897</v>
+        <v>6757355</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-10-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-06-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-10-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-06-30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Runt lämnade slaktrester från älgjakt.</t>
+          <t>140712171 / ART LEUC / Ej bedömd (0)  / OBJ.AREA:1 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,15 +765,125 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Ulf Ahlberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>80686732</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Storsjön, Bergby, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>606166</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6757514</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hamrånge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-10-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-10-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Runt lämnade slaktrester från älgjakt.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Göran Vesslén</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Göran Vesslén</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23257-2026 artfynd.xlsx
+++ b/artfynd/A 23257-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1913285</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80686732</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>